--- a/RuleTemplate.xlsx
+++ b/RuleTemplate.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="442">
   <si>
     <t>Name</t>
   </si>
@@ -1362,6 +1362,9 @@
   </si>
   <si>
     <t>IgnoreContext</t>
+  </si>
+  <si>
+    <t>FileSize</t>
   </si>
 </sst>
 </file>
@@ -6067,13 +6070,13 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8B7B4805-895C-4B4D-B437-049620AFDF29}">
           <x14:formula1>
-            <xm:f>ZZ_DataTab_ZZ!$B$1:$B$7</xm:f>
+            <xm:f>ZZ_DataTab_ZZ!$B$1:$B$9</xm:f>
           </x14:formula1>
           <xm:sqref>H1 H859:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7DD83A69-48FE-4200-9977-B732BAFDD123}">
           <x14:formula1>
-            <xm:f>ZZ_DataTab_ZZ!$B$1:$B$8</xm:f>
+            <xm:f>ZZ_DataTab_ZZ!$B$1:$B$9</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H858</xm:sqref>
         </x14:dataValidation>
@@ -6088,7 +6091,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
@@ -6146,6 +6149,11 @@
         <v>432</v>
       </c>
     </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>441</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/RuleTemplate.xlsx
+++ b/RuleTemplate.xlsx
@@ -1340,7 +1340,7 @@
     <t>RegexInline</t>
   </si>
   <si>
-    <t>(\w+[\.\?\!\:\;][^\s]\w+)|(\w+[\.\?\!\:\;]\s{2,}\w+)</t>
+    <t>([a-z]{2,}[.?!][A-Z][a-z]+)|(\w+[.?!:;]\s{2,}\w+)</t>
   </si>
   <si>
     <t>WCAG-2.0-1.1</t>
@@ -2854,7 +2854,7 @@
         <v>19</v>
       </c>
       <c r="I31" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1" t="s">
         <v>433</v>
